--- a/cards_template_excel.xlsx
+++ b/cards_template_excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Rust\ethan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9541C7A1-8B43-4FB0-B449-482F316B6868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00821319-6759-49B6-92FB-7AB5C32DB90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="160">
   <si>
     <t>Name</t>
   </si>
@@ -64,9 +64,6 @@
     <t>For The Glory</t>
   </si>
   <si>
-    <t>./assets/cards/ethan_allfire.png</t>
-  </si>
-  <si>
     <t>10th Anniversary Backer</t>
   </si>
   <si>
@@ -79,9 +76,6 @@
     <t>Kickstarter #1</t>
   </si>
   <si>
-    <t>./assets/cards/10th_anniversary_backer.png</t>
-  </si>
-  <si>
     <t>Abdominal Snowman</t>
   </si>
   <si>
@@ -94,33 +88,6 @@
     <t>Ice King Vs Marceline</t>
   </si>
   <si>
-    <t>./assets/cards/abdominal_snowman.png</t>
-  </si>
-  <si>
-    <t>./assets/cards/abnegator.png</t>
-  </si>
-  <si>
-    <t>./assets/cards/abraca_amadeus.png</t>
-  </si>
-  <si>
-    <t>./assets/cards/abracadaniel.png</t>
-  </si>
-  <si>
-    <t>./assets/cards/absorb_aether.png</t>
-  </si>
-  <si>
-    <t>./assets/cards/adorabunny.png</t>
-  </si>
-  <si>
-    <t>./assets/cards/adored_cobnoblin.png</t>
-  </si>
-  <si>
-    <t>./assets/cards/aeromancer.png</t>
-  </si>
-  <si>
-    <t>./assets/cards/albino_eyebat.png</t>
-  </si>
-  <si>
     <t>AbneGator</t>
   </si>
   <si>
@@ -202,9 +169,6 @@
     <t>Princess Bubblegum Vs Lumpy Space Princess</t>
   </si>
   <si>
-    <t>./assets/cards/amaizing_avalanche.png</t>
-  </si>
-  <si>
     <t>Amaizing Avalanche</t>
   </si>
   <si>
@@ -217,9 +181,6 @@
     <t>Ancient Comet</t>
   </si>
   <si>
-    <t>./assets/cards/ancient_comet.png</t>
-  </si>
-  <si>
     <t>Rainbow</t>
   </si>
   <si>
@@ -229,9 +190,6 @@
     <t>Ancient Healer</t>
   </si>
   <si>
-    <t>./assets/cards/ancient_healer.png</t>
-  </si>
-  <si>
     <t>If Ancient Healer is played on a facedown Landscape, turn it face up and heal 4 HP.</t>
   </si>
   <si>
@@ -244,9 +202,6 @@
     <t xml:space="preserve">When Ancient Magic Pharaoh Dragon enters or leaves play, shuffle your discard pile and swap it with your deck. </t>
   </si>
   <si>
-    <t>./assets/cards/ancient_magic_pharaoh_dragon.png</t>
-  </si>
-  <si>
     <t>Ancient Scholar</t>
   </si>
   <si>
@@ -256,61 +211,295 @@
     <t>Finn Vs Jake</t>
   </si>
   <si>
-    <t>./assets/cards/ancient_scholar.png</t>
-  </si>
-  <si>
     <t>Angel Heart</t>
   </si>
   <si>
     <t xml:space="preserve">While Angel Heart has exactly 3 damage on it, it has +3 ATK. </t>
   </si>
   <si>
-    <t>./assets/cards/angel_heart.png</t>
-  </si>
-  <si>
     <t>Angel of Chocolate</t>
   </si>
   <si>
     <t xml:space="preserve">Pay 1 Action &gt;&gt;&gt; Heal all damage from Angel of Chocolate. </t>
   </si>
   <si>
-    <t>./assets/cards/angel_of_chocolate.png</t>
-  </si>
-  <si>
     <t>Angel of Vanilla</t>
   </si>
   <si>
     <t xml:space="preserve">Pay 1 Action &gt;&gt;&gt; Heal all damage from Angel of Vanilla. </t>
   </si>
   <si>
-    <t>./assets/cards/angel_of_vanilla.png</t>
-  </si>
-  <si>
     <t>Apple Bully</t>
   </si>
   <si>
-    <t xml:space="preserve">Apple Bully's Landscape cannot be flipped face down by opponents. </t>
-  </si>
-  <si>
-    <t>./assets/cards/apple_bully.png</t>
-  </si>
-  <si>
     <t>Apple Pieclops</t>
   </si>
   <si>
-    <t xml:space="preserve">At the start of your turn, you may heal or deal 1 damage to each of your Creatures. (Choose for each Creature.) </t>
-  </si>
-  <si>
-    <t>./assets/cards/apple_pieclops.png</t>
-  </si>
-  <si>
     <t>Archer Dan</t>
   </si>
   <si>
     <t xml:space="preserve">FLOOP &gt;&gt;&gt; Destroy target Building in Archer Dan's Lane. </t>
   </si>
   <si>
-    <t>./assets/cards/archer_dan.png</t>
+    <t>Archer Danica</t>
+  </si>
+  <si>
+    <t>Fionna Vs Cake</t>
+  </si>
+  <si>
+    <t>archer_danica.png</t>
+  </si>
+  <si>
+    <t>Arctic Purge</t>
+  </si>
+  <si>
+    <t>Draw 2 cards. You may remove a non-damage token from a Creature or Landscape. If you do, your opponent discards a card.</t>
+  </si>
+  <si>
+    <t>FLOOP and destroy a Building you control &gt;&gt;&gt; Deal 3 damage to each opposing Creature.</t>
+  </si>
+  <si>
+    <t>At the start of your turn, you may heal or deal 1 damage to each of your Creatures. (Choose for each Creature.)</t>
+  </si>
+  <si>
+    <t>Apple Bully's Landscape cannot be flipped face down by opponents.</t>
+  </si>
+  <si>
+    <t>arctic_purge.png</t>
+  </si>
+  <si>
+    <t>ethan_allfire.png</t>
+  </si>
+  <si>
+    <t>10th_anniversary_backer.png</t>
+  </si>
+  <si>
+    <t>abdominal_snowman.png</t>
+  </si>
+  <si>
+    <t>abnegator.png</t>
+  </si>
+  <si>
+    <t>abraca_amadeus.png</t>
+  </si>
+  <si>
+    <t>abracadaniel.png</t>
+  </si>
+  <si>
+    <t>absorb_aether.png</t>
+  </si>
+  <si>
+    <t>adorabunny.png</t>
+  </si>
+  <si>
+    <t>adored_cobnoblin.png</t>
+  </si>
+  <si>
+    <t>aeromancer.png</t>
+  </si>
+  <si>
+    <t>albino_eyebat.png</t>
+  </si>
+  <si>
+    <t>amaizing_avalanche.png</t>
+  </si>
+  <si>
+    <t>ancient_comet.png</t>
+  </si>
+  <si>
+    <t>ancient_healer.png</t>
+  </si>
+  <si>
+    <t>ancient_magic_pharaoh_dragon.png</t>
+  </si>
+  <si>
+    <t>ancient_scholar.png</t>
+  </si>
+  <si>
+    <t>angel_heart.png</t>
+  </si>
+  <si>
+    <t>angel_of_chocolate.png</t>
+  </si>
+  <si>
+    <t>angel_of_vanilla.png</t>
+  </si>
+  <si>
+    <t>apple_bully.png</t>
+  </si>
+  <si>
+    <t>apple_pieclops.png</t>
+  </si>
+  <si>
+    <t>archer_dan.png</t>
+  </si>
+  <si>
+    <t>Ascension Silo</t>
+  </si>
+  <si>
+    <t>Building</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Once per turn, when your Creature in this Lane leaves play, draw 1 card. </t>
+  </si>
+  <si>
+    <t>ascension_silo.png</t>
+  </si>
+  <si>
+    <t>Ashcloud</t>
+  </si>
+  <si>
+    <t>LavaFlats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 damage to target opposing Creature and each opposing Creature in adjacent Lanes. </t>
+  </si>
+  <si>
+    <t>ashcloud.png</t>
+  </si>
+  <si>
+    <t>Assistance</t>
+  </si>
+  <si>
+    <t>Teamwork</t>
+  </si>
+  <si>
+    <t>At the start of your or your teammate's Fight Phase, if you or your teammate played a Creature with cost 2 or greater this turn, the other teammate may draw a card.</t>
+  </si>
+  <si>
+    <t>assistance.png</t>
+  </si>
+  <si>
+    <t>Auto-Plucker</t>
+  </si>
+  <si>
+    <t>FLOOP &gt;&gt;&gt; Heal or deal 1 damage to your Creature in this Lane.</t>
+  </si>
+  <si>
+    <t>auto-plucker.png</t>
+  </si>
+  <si>
+    <t>Axolotl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOOP &gt;&gt;&gt; Target player heals 3 HP. </t>
+  </si>
+  <si>
+    <t>Peppermint Butler Vs Magic Man</t>
+  </si>
+  <si>
+    <t>axolotl.png</t>
+  </si>
+  <si>
+    <t>Baby Finn &amp; Jake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your deck cannot contain Creatures with more than 3 ATK. At the start of your Fight Phase, choose one of your Creatures. That Creature has +3 ATK this turn. </t>
+  </si>
+  <si>
+    <t>baby_finn_&amp;_jake.png</t>
+  </si>
+  <si>
+    <t>Bail Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Put target Creature you own into your hand, then play it for free. </t>
+  </si>
+  <si>
+    <t>bail_out.png</t>
+  </si>
+  <si>
+    <t>Bale Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When target Creature attacks this turn, if it would leave play during the Fight Phase, remove all damage from it instead. </t>
+  </si>
+  <si>
+    <t>bale_out.png</t>
+  </si>
+  <si>
+    <t>Ban-She Princess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When Ban-She Princess enters play, you may remove a token from an adjacent Landscape. </t>
+  </si>
+  <si>
+    <t>ban-she_princess.png</t>
+  </si>
+  <si>
+    <t>Ban-She Queen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When Ban-She Queen enters play, you may remove a token from an adjacent Landscape. </t>
+  </si>
+  <si>
+    <t>ban-she_queen.png</t>
+  </si>
+  <si>
+    <t>Banana Man</t>
+  </si>
+  <si>
+    <t>banana_man.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Once per turn, you may peek at the bottom card of your deck and either discard it or put it on top of your deck. </t>
+  </si>
+  <si>
+    <t>Barrow Baron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrow Baron costs 1 less to play for every 5 cards in an opponent's discard pile. </t>
+  </si>
+  <si>
+    <t>Prismo Vs The Lich</t>
+  </si>
+  <si>
+    <t>barrow_baron.png</t>
+  </si>
+  <si>
+    <t>Basalt Behemoth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOOP &gt;&gt;&gt; Burn an opposing Creature, then deal 1 damage to that Creature for each burn token on Creatures in play. </t>
+  </si>
+  <si>
+    <t>basalt_behemoth.png</t>
+  </si>
+  <si>
+    <t>Bayou Boa</t>
+  </si>
+  <si>
+    <t>bayou_boa.png</t>
+  </si>
+  <si>
+    <t>Bayou Fountain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discard a card &gt;&gt;&gt; Your Creature in this Lane has +1 ATK this turn. </t>
+  </si>
+  <si>
+    <t>bayou_fountain.png</t>
+  </si>
+  <si>
+    <t>Bayou Surge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroy all Creatures in a Lane. Starting with you, each player may put a Creature from their hand into play on a Landscape they control in that Lane. </t>
+  </si>
+  <si>
+    <t>bayou_surge.png</t>
+  </si>
+  <si>
+    <t>Beach Ball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain 4 HP. Draw a card. You may put this into an opponent's hand. If you do, draw another card. (You may only play 1 Beach Ball per turn.) </t>
+  </si>
+  <si>
+    <t>beach_ball.png</t>
+  </si>
+  <si>
+    <t>Destroy a Creature you control &gt;&gt;&gt; Put 2 :attack_token: on Bayou Boa and heal 2 damage from it.</t>
   </si>
 </sst>
 </file>
@@ -665,14 +854,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.85546875" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="62.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="46" customWidth="1"/>
     <col min="7" max="9" width="10" customWidth="1"/>
   </cols>
@@ -723,7 +912,7 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -737,39 +926,39 @@
     </row>
     <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -783,22 +972,22 @@
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -812,22 +1001,22 @@
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -835,39 +1024,39 @@
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
         <v>38</v>
       </c>
-      <c r="B8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>49</v>
-      </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -875,22 +1064,22 @@
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -904,7 +1093,7 @@
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -913,13 +1102,13 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -933,22 +1122,22 @@
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
         <v>46</v>
       </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" t="s">
-        <v>57</v>
-      </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -962,22 +1151,22 @@
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
         <v>40</v>
       </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -991,22 +1180,22 @@
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1014,22 +1203,22 @@
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1037,22 +1226,22 @@
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
       <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
         <v>56</v>
       </c>
-      <c r="D15" t="s">
-        <v>70</v>
-      </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1066,22 +1255,22 @@
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1095,22 +1284,22 @@
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1124,22 +1313,22 @@
     </row>
     <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1153,22 +1342,22 @@
     </row>
     <row r="19" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F19" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1182,22 +1371,22 @@
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1211,7 +1400,7 @@
     </row>
     <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
@@ -1220,13 +1409,13 @@
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
         <v>13</v>
       </c>
       <c r="F21" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1240,22 +1429,22 @@
     </row>
     <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F22" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1269,7 +1458,7 @@
     </row>
     <row r="23" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
@@ -1278,13 +1467,13 @@
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F23" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1294,6 +1483,473 @@
       </c>
       <c r="I23">
         <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" t="s">
+        <v>107</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" t="s">
+        <v>111</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" t="s">
+        <v>120</v>
+      </c>
+      <c r="E30" t="s">
+        <v>121</v>
+      </c>
+      <c r="F30" t="s">
+        <v>122</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>132</v>
+      </c>
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" t="s">
+        <v>134</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" t="s">
+        <v>137</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>3</v>
+      </c>
+      <c r="I35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>138</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>140</v>
+      </c>
+      <c r="E36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>142</v>
+      </c>
+      <c r="E37" t="s">
+        <v>143</v>
+      </c>
+      <c r="F37" t="s">
+        <v>144</v>
+      </c>
+      <c r="G37">
+        <v>3</v>
+      </c>
+      <c r="H37">
+        <v>5</v>
+      </c>
+      <c r="I37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>145</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" t="s">
+        <v>147</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>148</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" t="s">
+        <v>159</v>
+      </c>
+      <c r="E39" t="s">
+        <v>39</v>
+      </c>
+      <c r="F39" t="s">
+        <v>149</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" t="s">
+        <v>151</v>
+      </c>
+      <c r="E40" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>154</v>
+      </c>
+      <c r="E41" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" t="s">
+        <v>155</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>156</v>
+      </c>
+      <c r="B42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E42" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" t="s">
+        <v>158</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/cards_template_excel.xlsx
+++ b/cards_template_excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Rust\ethan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23EE027-D82A-4D16-ACDE-3E77E2C71D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5A851C-BF38-4C1B-AFEF-DA4C3AA2EF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7524,16 +7524,16 @@
     <t>the_card_dweeb.jpg</t>
   </si>
   <si>
-    <t>kingpizzatime.jpg</t>
-  </si>
-  <si>
-    <t>jeffpattonmagic.jpg</t>
-  </si>
-  <si>
-    <t>pichuispro.jpg</t>
-  </si>
-  <si>
-    <t>notathotscott.jpg</t>
+    <t>kingpizzatime.jpg|kingpizzatime2.jpg</t>
+  </si>
+  <si>
+    <t>jeffpattonmagic.jpg|jeffpattonmagic2.jpg</t>
+  </si>
+  <si>
+    <t>pichuispro.jpg|pichuispro2.jpg</t>
+  </si>
+  <si>
+    <t>notathotscott.jpg|notathotscott2.jpg</t>
   </si>
 </sst>
 </file>

--- a/cards_template_excel.xlsx
+++ b/cards_template_excel.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84240D90-7A1C-496C-93C7-AB221100613E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Лист1" state="visible" r:id="rId4"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4940" uniqueCount="2506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4951" uniqueCount="2511">
   <si>
     <t>Name</t>
   </si>
@@ -7516,9 +7517,6 @@
     <t>pichuispro.jpg|pichuispro2.jpg</t>
   </si>
   <si>
-    <t>NotAThotScott</t>
-  </si>
-  <si>
     <t xml:space="preserve">When TailGator enters play, draw a card for each Creature placed into your discard pile this turn. </t>
   </si>
   <si>
@@ -7532,33 +7530,51 @@
   </si>
   <si>
     <t>toilet_of_doom_ftg.jpg</t>
+  </si>
+  <si>
+    <t>NotAThotScott Billy</t>
+  </si>
+  <si>
+    <t>NotAThotScott TailGator</t>
+  </si>
+  <si>
+    <t>notathotscott_billy.jpg</t>
+  </si>
+  <si>
+    <t>Zoë</t>
+  </si>
+  <si>
+    <t>Custom Alternative Art</t>
+  </si>
+  <si>
+    <t>zoe.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -7872,15 +7888,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I834"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I836"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.7109375" customWidth="1"/>
-    <col min="4" max="4" width="82.5703125" customWidth="1"/>
+    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="4" max="4" width="82.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7909,7 +7925,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7930,7 +7946,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -7951,7 +7967,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -7980,7 +7996,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -8009,7 +8025,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -8038,7 +8054,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -8067,7 +8083,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -8096,7 +8112,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -8125,7 +8141,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -8154,7 +8170,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -8183,7 +8199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -8212,7 +8228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -8238,7 +8254,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -8267,7 +8283,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -8293,7 +8309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -8322,7 +8338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -8351,7 +8367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>61</v>
       </c>
@@ -8380,7 +8396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -8409,7 +8425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -8438,7 +8454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>70</v>
       </c>
@@ -8467,7 +8483,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -8496,7 +8512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>76</v>
       </c>
@@ -8525,7 +8541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -8551,7 +8567,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -8580,7 +8596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>84</v>
       </c>
@@ -8609,7 +8625,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>87</v>
       </c>
@@ -8638,7 +8654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>90</v>
       </c>
@@ -8667,7 +8683,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>93</v>
       </c>
@@ -8696,7 +8712,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>96</v>
       </c>
@@ -8725,7 +8741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>99</v>
       </c>
@@ -8754,7 +8770,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>102</v>
       </c>
@@ -8783,7 +8799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>105</v>
       </c>
@@ -8812,7 +8828,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -8841,7 +8857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>111</v>
       </c>
@@ -8866,7 +8882,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>115</v>
       </c>
@@ -8891,7 +8907,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -8916,7 +8932,7 @@
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -8941,7 +8957,7 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>124</v>
       </c>
@@ -8966,7 +8982,7 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>127</v>
       </c>
@@ -8991,7 +9007,7 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>130</v>
       </c>
@@ -9016,7 +9032,7 @@
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>133</v>
       </c>
@@ -9041,7 +9057,7 @@
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>135</v>
       </c>
@@ -9066,7 +9082,7 @@
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>138</v>
       </c>
@@ -9091,7 +9107,7 @@
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>142</v>
       </c>
@@ -9116,7 +9132,7 @@
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -9141,7 +9157,7 @@
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>148</v>
       </c>
@@ -9166,7 +9182,7 @@
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>151</v>
       </c>
@@ -9191,7 +9207,7 @@
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>154</v>
       </c>
@@ -9212,7 +9228,7 @@
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>158</v>
       </c>
@@ -9233,7 +9249,7 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>161</v>
       </c>
@@ -9262,7 +9278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>165</v>
       </c>
@@ -9288,7 +9304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>167</v>
       </c>
@@ -9317,7 +9333,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>171</v>
       </c>
@@ -9346,7 +9362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>174</v>
       </c>
@@ -9375,7 +9391,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>177</v>
       </c>
@@ -9404,7 +9420,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>180</v>
       </c>
@@ -9433,7 +9449,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>183</v>
       </c>
@@ -9462,7 +9478,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>186</v>
       </c>
@@ -9491,7 +9507,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>189</v>
       </c>
@@ -9520,7 +9536,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>192</v>
       </c>
@@ -9549,7 +9565,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>195</v>
       </c>
@@ -9578,7 +9594,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>198</v>
       </c>
@@ -9607,7 +9623,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>201</v>
       </c>
@@ -9636,7 +9652,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>204</v>
       </c>
@@ -9665,7 +9681,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>207</v>
       </c>
@@ -9694,7 +9710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>210</v>
       </c>
@@ -9723,7 +9739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>213</v>
       </c>
@@ -9752,7 +9768,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>216</v>
       </c>
@@ -9781,7 +9797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>219</v>
       </c>
@@ -9807,7 +9823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>221</v>
       </c>
@@ -9836,7 +9852,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>224</v>
       </c>
@@ -9865,7 +9881,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>227</v>
       </c>
@@ -9894,7 +9910,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>230</v>
       </c>
@@ -9923,7 +9939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>233</v>
       </c>
@@ -9952,7 +9968,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>236</v>
       </c>
@@ -9981,7 +9997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>239</v>
       </c>
@@ -10010,7 +10026,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>242</v>
       </c>
@@ -10039,7 +10055,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>245</v>
       </c>
@@ -10068,7 +10084,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>248</v>
       </c>
@@ -10097,7 +10113,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>251</v>
       </c>
@@ -10126,7 +10142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>254</v>
       </c>
@@ -10151,7 +10167,7 @@
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>257</v>
       </c>
@@ -10176,7 +10192,7 @@
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>260</v>
       </c>
@@ -10201,7 +10217,7 @@
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>263</v>
       </c>
@@ -10226,7 +10242,7 @@
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>266</v>
       </c>
@@ -10251,7 +10267,7 @@
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>269</v>
       </c>
@@ -10276,7 +10292,7 @@
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>272</v>
       </c>
@@ -10301,7 +10317,7 @@
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>275</v>
       </c>
@@ -10326,7 +10342,7 @@
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>278</v>
       </c>
@@ -10351,7 +10367,7 @@
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>281</v>
       </c>
@@ -10376,7 +10392,7 @@
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>284</v>
       </c>
@@ -10401,7 +10417,7 @@
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>287</v>
       </c>
@@ -10422,7 +10438,7 @@
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>291</v>
       </c>
@@ -10443,7 +10459,7 @@
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>294</v>
       </c>
@@ -10472,7 +10488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>298</v>
       </c>
@@ -10501,7 +10517,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>301</v>
       </c>
@@ -10530,7 +10546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>304</v>
       </c>
@@ -10559,7 +10575,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>307</v>
       </c>
@@ -10588,7 +10604,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>310</v>
       </c>
@@ -10617,7 +10633,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>313</v>
       </c>
@@ -10646,7 +10662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>316</v>
       </c>
@@ -10675,7 +10691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>319</v>
       </c>
@@ -10701,7 +10717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>321</v>
       </c>
@@ -10730,7 +10746,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>324</v>
       </c>
@@ -10759,7 +10775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>327</v>
       </c>
@@ -10788,7 +10804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>330</v>
       </c>
@@ -10817,7 +10833,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>333</v>
       </c>
@@ -10846,7 +10862,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>336</v>
       </c>
@@ -10875,7 +10891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>339</v>
       </c>
@@ -10904,7 +10920,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>342</v>
       </c>
@@ -10933,7 +10949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>345</v>
       </c>
@@ -10962,7 +10978,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>348</v>
       </c>
@@ -10991,7 +11007,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>351</v>
       </c>
@@ -11020,7 +11036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>354</v>
       </c>
@@ -11049,7 +11065,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>357</v>
       </c>
@@ -11078,7 +11094,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>360</v>
       </c>
@@ -11107,7 +11123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>363</v>
       </c>
@@ -11136,7 +11152,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>366</v>
       </c>
@@ -11165,7 +11181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>369</v>
       </c>
@@ -11194,7 +11210,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>372</v>
       </c>
@@ -11223,7 +11239,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>375</v>
       </c>
@@ -11252,7 +11268,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>378</v>
       </c>
@@ -11281,7 +11297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>381</v>
       </c>
@@ -11310,7 +11326,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>384</v>
       </c>
@@ -11339,7 +11355,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>387</v>
       </c>
@@ -11364,7 +11380,7 @@
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>390</v>
       </c>
@@ -11389,7 +11405,7 @@
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>393</v>
       </c>
@@ -11414,7 +11430,7 @@
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>396</v>
       </c>
@@ -11439,7 +11455,7 @@
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>399</v>
       </c>
@@ -11464,7 +11480,7 @@
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>402</v>
       </c>
@@ -11489,7 +11505,7 @@
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>405</v>
       </c>
@@ -11514,7 +11530,7 @@
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>408</v>
       </c>
@@ -11539,7 +11555,7 @@
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>411</v>
       </c>
@@ -11564,7 +11580,7 @@
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>414</v>
       </c>
@@ -11589,7 +11605,7 @@
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>417</v>
       </c>
@@ -11614,7 +11630,7 @@
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>420</v>
       </c>
@@ -11639,7 +11655,7 @@
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>423</v>
       </c>
@@ -11664,7 +11680,7 @@
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>426</v>
       </c>
@@ -11689,7 +11705,7 @@
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>429</v>
       </c>
@@ -11714,7 +11730,7 @@
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>432</v>
       </c>
@@ -11739,7 +11755,7 @@
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>435</v>
       </c>
@@ -11760,7 +11776,7 @@
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>439</v>
       </c>
@@ -11781,7 +11797,7 @@
       <c r="H143" s="2"/>
       <c r="I143" s="2"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>442</v>
       </c>
@@ -11810,7 +11826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>445</v>
       </c>
@@ -11839,7 +11855,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>448</v>
       </c>
@@ -11868,7 +11884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>451</v>
       </c>
@@ -11897,7 +11913,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>454</v>
       </c>
@@ -11926,7 +11942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>457</v>
       </c>
@@ -11955,7 +11971,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>460</v>
       </c>
@@ -11984,7 +12000,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>463</v>
       </c>
@@ -12013,7 +12029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>465</v>
       </c>
@@ -12042,7 +12058,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>468</v>
       </c>
@@ -12071,7 +12087,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>471</v>
       </c>
@@ -12100,7 +12116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>474</v>
       </c>
@@ -12129,7 +12145,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>477</v>
       </c>
@@ -12158,7 +12174,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>480</v>
       </c>
@@ -12187,7 +12203,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>483</v>
       </c>
@@ -12216,7 +12232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>486</v>
       </c>
@@ -12245,7 +12261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>488</v>
       </c>
@@ -12274,7 +12290,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>490</v>
       </c>
@@ -12303,7 +12319,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>493</v>
       </c>
@@ -12332,7 +12348,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>496</v>
       </c>
@@ -12361,7 +12377,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>499</v>
       </c>
@@ -12390,7 +12406,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>502</v>
       </c>
@@ -12419,7 +12435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>505</v>
       </c>
@@ -12448,7 +12464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>508</v>
       </c>
@@ -12477,7 +12493,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>511</v>
       </c>
@@ -12506,7 +12522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>514</v>
       </c>
@@ -12535,7 +12551,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>517</v>
       </c>
@@ -12561,7 +12577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>519</v>
       </c>
@@ -12590,7 +12606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>522</v>
       </c>
@@ -12619,7 +12635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>525</v>
       </c>
@@ -12644,7 +12660,7 @@
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>528</v>
       </c>
@@ -12669,7 +12685,7 @@
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>531</v>
       </c>
@@ -12694,7 +12710,7 @@
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>534</v>
       </c>
@@ -12719,7 +12735,7 @@
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>537</v>
       </c>
@@ -12744,7 +12760,7 @@
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>540</v>
       </c>
@@ -12769,7 +12785,7 @@
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>543</v>
       </c>
@@ -12794,7 +12810,7 @@
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>546</v>
       </c>
@@ -12819,7 +12835,7 @@
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>549</v>
       </c>
@@ -12844,7 +12860,7 @@
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>552</v>
       </c>
@@ -12869,7 +12885,7 @@
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>555</v>
       </c>
@@ -12894,7 +12910,7 @@
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>558</v>
       </c>
@@ -12919,7 +12935,7 @@
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>561</v>
       </c>
@@ -12944,7 +12960,7 @@
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>564</v>
       </c>
@@ -12969,7 +12985,7 @@
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>567</v>
       </c>
@@ -12994,7 +13010,7 @@
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>570</v>
       </c>
@@ -13019,7 +13035,7 @@
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>573</v>
       </c>
@@ -13044,7 +13060,7 @@
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>576</v>
       </c>
@@ -13065,7 +13081,7 @@
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>580</v>
       </c>
@@ -13086,7 +13102,7 @@
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>583</v>
       </c>
@@ -13115,7 +13131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>586</v>
       </c>
@@ -13144,7 +13160,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>589</v>
       </c>
@@ -13173,7 +13189,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>592</v>
       </c>
@@ -13202,7 +13218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>594</v>
       </c>
@@ -13231,7 +13247,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>597</v>
       </c>
@@ -13260,7 +13276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>600</v>
       </c>
@@ -13289,7 +13305,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>603</v>
       </c>
@@ -13318,7 +13334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>605</v>
       </c>
@@ -13347,7 +13363,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>608</v>
       </c>
@@ -13376,7 +13392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>611</v>
       </c>
@@ -13405,7 +13421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>614</v>
       </c>
@@ -13434,7 +13450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>617</v>
       </c>
@@ -13463,7 +13479,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>620</v>
       </c>
@@ -13492,7 +13508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>623</v>
       </c>
@@ -13521,7 +13537,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>625</v>
       </c>
@@ -13550,7 +13566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>628</v>
       </c>
@@ -13579,7 +13595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>631</v>
       </c>
@@ -13608,7 +13624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>634</v>
       </c>
@@ -13637,7 +13653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>637</v>
       </c>
@@ -13666,7 +13682,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>640</v>
       </c>
@@ -13695,7 +13711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>644</v>
       </c>
@@ -13724,7 +13740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>646</v>
       </c>
@@ -13753,7 +13769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>649</v>
       </c>
@@ -13782,7 +13798,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>652</v>
       </c>
@@ -13811,7 +13827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>655</v>
       </c>
@@ -13840,7 +13856,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>658</v>
       </c>
@@ -13869,7 +13885,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>661</v>
       </c>
@@ -13898,7 +13914,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>664</v>
       </c>
@@ -13927,7 +13943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>667</v>
       </c>
@@ -13956,7 +13972,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>670</v>
       </c>
@@ -13985,7 +14001,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>673</v>
       </c>
@@ -14014,7 +14030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>676</v>
       </c>
@@ -14039,7 +14055,7 @@
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>679</v>
       </c>
@@ -14064,7 +14080,7 @@
       <c r="H225" s="2"/>
       <c r="I225" s="2"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>682</v>
       </c>
@@ -14089,7 +14105,7 @@
       <c r="H226" s="2"/>
       <c r="I226" s="2"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>685</v>
       </c>
@@ -14114,7 +14130,7 @@
       <c r="H227" s="2"/>
       <c r="I227" s="2"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>688</v>
       </c>
@@ -14139,7 +14155,7 @@
       <c r="H228" s="2"/>
       <c r="I228" s="2"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>691</v>
       </c>
@@ -14164,7 +14180,7 @@
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>694</v>
       </c>
@@ -14189,7 +14205,7 @@
       <c r="H230" s="2"/>
       <c r="I230" s="2"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>697</v>
       </c>
@@ -14214,7 +14230,7 @@
       <c r="H231" s="2"/>
       <c r="I231" s="2"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>700</v>
       </c>
@@ -14239,7 +14255,7 @@
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>703</v>
       </c>
@@ -14264,7 +14280,7 @@
       <c r="H233" s="2"/>
       <c r="I233" s="2"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>706</v>
       </c>
@@ -14289,7 +14305,7 @@
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>709</v>
       </c>
@@ -14314,7 +14330,7 @@
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>712</v>
       </c>
@@ -14339,7 +14355,7 @@
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>715</v>
       </c>
@@ -14364,7 +14380,7 @@
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>718</v>
       </c>
@@ -14389,7 +14405,7 @@
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>721</v>
       </c>
@@ -14414,7 +14430,7 @@
       <c r="H239" s="2"/>
       <c r="I239" s="2"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>724</v>
       </c>
@@ -14439,7 +14455,7 @@
       <c r="H240" s="2"/>
       <c r="I240" s="2"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>727</v>
       </c>
@@ -14464,7 +14480,7 @@
       <c r="H241" s="2"/>
       <c r="I241" s="2"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>730</v>
       </c>
@@ -14489,7 +14505,7 @@
       <c r="H242" s="2"/>
       <c r="I242" s="2"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>733</v>
       </c>
@@ -14514,7 +14530,7 @@
       <c r="H243" s="2"/>
       <c r="I243" s="2"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>736</v>
       </c>
@@ -14539,7 +14555,7 @@
       <c r="H244" s="2"/>
       <c r="I244" s="2"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>739</v>
       </c>
@@ -14560,7 +14576,7 @@
       <c r="H245" s="2"/>
       <c r="I245" s="2"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>743</v>
       </c>
@@ -14581,7 +14597,7 @@
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>746</v>
       </c>
@@ -14610,7 +14626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>749</v>
       </c>
@@ -14639,7 +14655,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>752</v>
       </c>
@@ -14668,7 +14684,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>755</v>
       </c>
@@ -14697,7 +14713,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>758</v>
       </c>
@@ -14726,7 +14742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>761</v>
       </c>
@@ -14755,7 +14771,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>764</v>
       </c>
@@ -14784,7 +14800,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>767</v>
       </c>
@@ -14813,7 +14829,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>770</v>
       </c>
@@ -14842,7 +14858,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>773</v>
       </c>
@@ -14871,7 +14887,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>776</v>
       </c>
@@ -14900,7 +14916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>779</v>
       </c>
@@ -14929,7 +14945,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>782</v>
       </c>
@@ -14958,7 +14974,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>785</v>
       </c>
@@ -14987,7 +15003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>788</v>
       </c>
@@ -15016,7 +15032,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>791</v>
       </c>
@@ -15045,7 +15061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>794</v>
       </c>
@@ -15071,7 +15087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>796</v>
       </c>
@@ -15100,7 +15116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>799</v>
       </c>
@@ -15129,7 +15145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>802</v>
       </c>
@@ -15158,7 +15174,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>805</v>
       </c>
@@ -15187,7 +15203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>808</v>
       </c>
@@ -15216,7 +15232,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>811</v>
       </c>
@@ -15245,7 +15261,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>813</v>
       </c>
@@ -15274,7 +15290,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>816</v>
       </c>
@@ -15303,7 +15319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>819</v>
       </c>
@@ -15332,7 +15348,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>822</v>
       </c>
@@ -15361,7 +15377,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>825</v>
       </c>
@@ -15390,7 +15406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>828</v>
       </c>
@@ -15419,7 +15435,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>831</v>
       </c>
@@ -15445,7 +15461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>833</v>
       </c>
@@ -15470,7 +15486,7 @@
       <c r="H277" s="2"/>
       <c r="I277" s="2"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>836</v>
       </c>
@@ -15495,7 +15511,7 @@
       <c r="H278" s="2"/>
       <c r="I278" s="2"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>839</v>
       </c>
@@ -15520,7 +15536,7 @@
       <c r="H279" s="2"/>
       <c r="I279" s="2"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>842</v>
       </c>
@@ -15545,7 +15561,7 @@
       <c r="H280" s="2"/>
       <c r="I280" s="2"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>845</v>
       </c>
@@ -15570,7 +15586,7 @@
       <c r="H281" s="2"/>
       <c r="I281" s="2"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>848</v>
       </c>
@@ -15595,7 +15611,7 @@
       <c r="H282" s="2"/>
       <c r="I282" s="2"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>851</v>
       </c>
@@ -15620,7 +15636,7 @@
       <c r="H283" s="2"/>
       <c r="I283" s="2"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>854</v>
       </c>
@@ -15645,7 +15661,7 @@
       <c r="H284" s="2"/>
       <c r="I284" s="2"/>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>857</v>
       </c>
@@ -15670,7 +15686,7 @@
       <c r="H285" s="2"/>
       <c r="I285" s="2"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>860</v>
       </c>
@@ -15695,7 +15711,7 @@
       <c r="H286" s="2"/>
       <c r="I286" s="2"/>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>863</v>
       </c>
@@ -15720,7 +15736,7 @@
       <c r="H287" s="2"/>
       <c r="I287" s="2"/>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>866</v>
       </c>
@@ -15745,7 +15761,7 @@
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>869</v>
       </c>
@@ -15770,7 +15786,7 @@
       <c r="H289" s="2"/>
       <c r="I289" s="2"/>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>872</v>
       </c>
@@ -15795,7 +15811,7 @@
       <c r="H290" s="2"/>
       <c r="I290" s="2"/>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>875</v>
       </c>
@@ -15820,7 +15836,7 @@
       <c r="H291" s="2"/>
       <c r="I291" s="2"/>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>878</v>
       </c>
@@ -15845,7 +15861,7 @@
       <c r="H292" s="2"/>
       <c r="I292" s="2"/>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>881</v>
       </c>
@@ -15870,7 +15886,7 @@
       <c r="H293" s="2"/>
       <c r="I293" s="2"/>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>884</v>
       </c>
@@ -15895,7 +15911,7 @@
       <c r="H294" s="2"/>
       <c r="I294" s="2"/>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>887</v>
       </c>
@@ -15916,7 +15932,7 @@
       <c r="H295" s="2"/>
       <c r="I295" s="2"/>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>890</v>
       </c>
@@ -15937,7 +15953,7 @@
       <c r="H296" s="2"/>
       <c r="I296" s="2"/>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>893</v>
       </c>
@@ -15958,7 +15974,7 @@
       <c r="H297" s="2"/>
       <c r="I297" s="2"/>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>896</v>
       </c>
@@ -15979,7 +15995,7 @@
       <c r="H298" s="2"/>
       <c r="I298" s="2"/>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>899</v>
       </c>
@@ -16008,7 +16024,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>902</v>
       </c>
@@ -16037,7 +16053,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>905</v>
       </c>
@@ -16066,7 +16082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>908</v>
       </c>
@@ -16095,7 +16111,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>911</v>
       </c>
@@ -16124,7 +16140,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>914</v>
       </c>
@@ -16153,7 +16169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>917</v>
       </c>
@@ -16182,7 +16198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>920</v>
       </c>
@@ -16211,7 +16227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>923</v>
       </c>
@@ -16240,7 +16256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>926</v>
       </c>
@@ -16269,7 +16285,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>929</v>
       </c>
@@ -16298,7 +16314,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>932</v>
       </c>
@@ -16327,7 +16343,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>935</v>
       </c>
@@ -16356,7 +16372,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>938</v>
       </c>
@@ -16385,7 +16401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>941</v>
       </c>
@@ -16414,7 +16430,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>944</v>
       </c>
@@ -16443,7 +16459,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>947</v>
       </c>
@@ -16469,7 +16485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>949</v>
       </c>
@@ -16498,7 +16514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>952</v>
       </c>
@@ -16527,7 +16543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>955</v>
       </c>
@@ -16556,7 +16572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>958</v>
       </c>
@@ -16585,7 +16601,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>961</v>
       </c>
@@ -16614,7 +16630,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>964</v>
       </c>
@@ -16643,7 +16659,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>967</v>
       </c>
@@ -16672,7 +16688,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>970</v>
       </c>
@@ -16701,7 +16717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>973</v>
       </c>
@@ -16730,7 +16746,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>976</v>
       </c>
@@ -16759,7 +16775,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>979</v>
       </c>
@@ -16788,7 +16804,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>982</v>
       </c>
@@ -16817,7 +16833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>985</v>
       </c>
@@ -16846,7 +16862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>988</v>
       </c>
@@ -16875,7 +16891,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>991</v>
       </c>
@@ -16904,7 +16920,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>994</v>
       </c>
@@ -16933,7 +16949,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>997</v>
       </c>
@@ -16962,7 +16978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>1000</v>
       </c>
@@ -16991,7 +17007,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>1003</v>
       </c>
@@ -17020,7 +17036,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>1006</v>
       </c>
@@ -17049,7 +17065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>1009</v>
       </c>
@@ -17078,7 +17094,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>1012</v>
       </c>
@@ -17107,7 +17123,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>1015</v>
       </c>
@@ -17136,7 +17152,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>1018</v>
       </c>
@@ -17165,7 +17181,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>1021</v>
       </c>
@@ -17194,7 +17210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>1024</v>
       </c>
@@ -17223,7 +17239,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>1027</v>
       </c>
@@ -17252,7 +17268,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>1030</v>
       </c>
@@ -17281,7 +17297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>1033</v>
       </c>
@@ -17310,7 +17326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>1036</v>
       </c>
@@ -17339,7 +17355,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>1039</v>
       </c>
@@ -17368,7 +17384,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1042</v>
       </c>
@@ -17397,7 +17413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>1045</v>
       </c>
@@ -17426,7 +17442,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>1048</v>
       </c>
@@ -17455,7 +17471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>1051</v>
       </c>
@@ -17484,7 +17500,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>1054</v>
       </c>
@@ -17513,7 +17529,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>1057</v>
       </c>
@@ -17542,7 +17558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>1060</v>
       </c>
@@ -17571,7 +17587,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>1063</v>
       </c>
@@ -17600,7 +17616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>1066</v>
       </c>
@@ -17629,7 +17645,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>1069</v>
       </c>
@@ -17658,7 +17674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>1072</v>
       </c>
@@ -17683,7 +17699,7 @@
       <c r="H357" s="2"/>
       <c r="I357" s="2"/>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>1075</v>
       </c>
@@ -17708,7 +17724,7 @@
       <c r="H358" s="2"/>
       <c r="I358" s="2"/>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>1078</v>
       </c>
@@ -17733,7 +17749,7 @@
       <c r="H359" s="2"/>
       <c r="I359" s="2"/>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>1081</v>
       </c>
@@ -17758,7 +17774,7 @@
       <c r="H360" s="2"/>
       <c r="I360" s="2"/>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>1084</v>
       </c>
@@ -17783,7 +17799,7 @@
       <c r="H361" s="2"/>
       <c r="I361" s="2"/>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>1087</v>
       </c>
@@ -17808,7 +17824,7 @@
       <c r="H362" s="2"/>
       <c r="I362" s="2"/>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>1090</v>
       </c>
@@ -17833,7 +17849,7 @@
       <c r="H363" s="2"/>
       <c r="I363" s="2"/>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>1093</v>
       </c>
@@ -17858,7 +17874,7 @@
       <c r="H364" s="2"/>
       <c r="I364" s="2"/>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>1096</v>
       </c>
@@ -17883,7 +17899,7 @@
       <c r="H365" s="2"/>
       <c r="I365" s="2"/>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>1099</v>
       </c>
@@ -17908,7 +17924,7 @@
       <c r="H366" s="2"/>
       <c r="I366" s="2"/>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>1102</v>
       </c>
@@ -17933,7 +17949,7 @@
       <c r="H367" s="2"/>
       <c r="I367" s="2"/>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>1105</v>
       </c>
@@ -17958,7 +17974,7 @@
       <c r="H368" s="2"/>
       <c r="I368" s="2"/>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>1108</v>
       </c>
@@ -17983,7 +17999,7 @@
       <c r="H369" s="2"/>
       <c r="I369" s="2"/>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>1111</v>
       </c>
@@ -18008,7 +18024,7 @@
       <c r="H370" s="2"/>
       <c r="I370" s="2"/>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>1114</v>
       </c>
@@ -18033,7 +18049,7 @@
       <c r="H371" s="2"/>
       <c r="I371" s="2"/>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>1117</v>
       </c>
@@ -18058,7 +18074,7 @@
       <c r="H372" s="2"/>
       <c r="I372" s="2"/>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>1120</v>
       </c>
@@ -18083,7 +18099,7 @@
       <c r="H373" s="2"/>
       <c r="I373" s="2"/>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>1123</v>
       </c>
@@ -18108,7 +18124,7 @@
       <c r="H374" s="2"/>
       <c r="I374" s="2"/>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>1126</v>
       </c>
@@ -18133,7 +18149,7 @@
       <c r="H375" s="2"/>
       <c r="I375" s="2"/>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>1129</v>
       </c>
@@ -18158,7 +18174,7 @@
       <c r="H376" s="2"/>
       <c r="I376" s="2"/>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>1132</v>
       </c>
@@ -18183,7 +18199,7 @@
       <c r="H377" s="2"/>
       <c r="I377" s="2"/>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>1135</v>
       </c>
@@ -18208,7 +18224,7 @@
       <c r="H378" s="2"/>
       <c r="I378" s="2"/>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>1138</v>
       </c>
@@ -18233,7 +18249,7 @@
       <c r="H379" s="2"/>
       <c r="I379" s="2"/>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>1141</v>
       </c>
@@ -18258,7 +18274,7 @@
       <c r="H380" s="2"/>
       <c r="I380" s="2"/>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>1144</v>
       </c>
@@ -18283,7 +18299,7 @@
       <c r="H381" s="2"/>
       <c r="I381" s="2"/>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>1147</v>
       </c>
@@ -18308,7 +18324,7 @@
       <c r="H382" s="2"/>
       <c r="I382" s="2"/>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>1150</v>
       </c>
@@ -18333,7 +18349,7 @@
       <c r="H383" s="2"/>
       <c r="I383" s="2"/>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>1153</v>
       </c>
@@ -18358,7 +18374,7 @@
       <c r="H384" s="2"/>
       <c r="I384" s="2"/>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>1156</v>
       </c>
@@ -18383,7 +18399,7 @@
       <c r="H385" s="2"/>
       <c r="I385" s="2"/>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>1160</v>
       </c>
@@ -18408,7 +18424,7 @@
       <c r="H386" s="2"/>
       <c r="I386" s="2"/>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>1163</v>
       </c>
@@ -18433,7 +18449,7 @@
       <c r="H387" s="2"/>
       <c r="I387" s="2"/>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>1166</v>
       </c>
@@ -18458,7 +18474,7 @@
       <c r="H388" s="2"/>
       <c r="I388" s="2"/>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>1169</v>
       </c>
@@ -18483,7 +18499,7 @@
       <c r="H389" s="2"/>
       <c r="I389" s="2"/>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>1172</v>
       </c>
@@ -18508,7 +18524,7 @@
       <c r="H390" s="2"/>
       <c r="I390" s="2"/>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>1175</v>
       </c>
@@ -18533,7 +18549,7 @@
       <c r="H391" s="2"/>
       <c r="I391" s="2"/>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>1178</v>
       </c>
@@ -18558,7 +18574,7 @@
       <c r="H392" s="2"/>
       <c r="I392" s="2"/>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>1181</v>
       </c>
@@ -18583,7 +18599,7 @@
       <c r="H393" s="2"/>
       <c r="I393" s="2"/>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>1184</v>
       </c>
@@ -18608,7 +18624,7 @@
       <c r="H394" s="2"/>
       <c r="I394" s="2"/>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>1187</v>
       </c>
@@ -18633,7 +18649,7 @@
       <c r="H395" s="2"/>
       <c r="I395" s="2"/>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>1190</v>
       </c>
@@ -18658,7 +18674,7 @@
       <c r="H396" s="2"/>
       <c r="I396" s="2"/>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>1193</v>
       </c>
@@ -18683,7 +18699,7 @@
       <c r="H397" s="2"/>
       <c r="I397" s="2"/>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>1196</v>
       </c>
@@ -18708,7 +18724,7 @@
       <c r="H398" s="2"/>
       <c r="I398" s="2"/>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>1199</v>
       </c>
@@ -18733,7 +18749,7 @@
       <c r="H399" s="2"/>
       <c r="I399" s="2"/>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>1202</v>
       </c>
@@ -18758,7 +18774,7 @@
       <c r="H400" s="2"/>
       <c r="I400" s="2"/>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>1205</v>
       </c>
@@ -18783,7 +18799,7 @@
       <c r="H401" s="2"/>
       <c r="I401" s="2"/>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>1208</v>
       </c>
@@ -18808,7 +18824,7 @@
       <c r="H402" s="2"/>
       <c r="I402" s="2"/>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>1211</v>
       </c>
@@ -18833,7 +18849,7 @@
       <c r="H403" s="2"/>
       <c r="I403" s="2"/>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>1214</v>
       </c>
@@ -18858,7 +18874,7 @@
       <c r="H404" s="2"/>
       <c r="I404" s="2"/>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>1217</v>
       </c>
@@ -18883,7 +18899,7 @@
       <c r="H405" s="2"/>
       <c r="I405" s="2"/>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>1220</v>
       </c>
@@ -18908,7 +18924,7 @@
       <c r="H406" s="2"/>
       <c r="I406" s="2"/>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>1223</v>
       </c>
@@ -18937,7 +18953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>1227</v>
       </c>
@@ -18966,7 +18982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>1230</v>
       </c>
@@ -18995,7 +19011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>1233</v>
       </c>
@@ -19024,7 +19040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>1236</v>
       </c>
@@ -19053,7 +19069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>1239</v>
       </c>
@@ -19082,7 +19098,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>1242</v>
       </c>
@@ -19111,7 +19127,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>1245</v>
       </c>
@@ -19140,7 +19156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>1248</v>
       </c>
@@ -19169,7 +19185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>1251</v>
       </c>
@@ -19198,7 +19214,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>1254</v>
       </c>
@@ -19227,7 +19243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>1256</v>
       </c>
@@ -19256,7 +19272,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>1259</v>
       </c>
@@ -19285,7 +19301,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>1262</v>
       </c>
@@ -19314,7 +19330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>1265</v>
       </c>
@@ -19343,7 +19359,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>1268</v>
       </c>
@@ -19372,7 +19388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>1271</v>
       </c>
@@ -19401,7 +19417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>1274</v>
       </c>
@@ -19430,7 +19446,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>1277</v>
       </c>
@@ -19459,7 +19475,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>1280</v>
       </c>
@@ -19488,7 +19504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>1283</v>
       </c>
@@ -19517,7 +19533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>1286</v>
       </c>
@@ -19546,7 +19562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>1289</v>
       </c>
@@ -19575,7 +19591,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>1292</v>
       </c>
@@ -19604,7 +19620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>1295</v>
       </c>
@@ -19633,7 +19649,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>1298</v>
       </c>
@@ -19662,7 +19678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>1301</v>
       </c>
@@ -19691,7 +19707,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>1304</v>
       </c>
@@ -19720,7 +19736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>1307</v>
       </c>
@@ -19749,7 +19765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>1310</v>
       </c>
@@ -19778,7 +19794,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>1313</v>
       </c>
@@ -19807,7 +19823,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>1316</v>
       </c>
@@ -19836,7 +19852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>1319</v>
       </c>
@@ -19865,7 +19881,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>1322</v>
       </c>
@@ -19894,7 +19910,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>1325</v>
       </c>
@@ -19923,7 +19939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>1327</v>
       </c>
@@ -19952,7 +19968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>1330</v>
       </c>
@@ -19981,7 +19997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>1333</v>
       </c>
@@ -20010,7 +20026,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>1336</v>
       </c>
@@ -20039,7 +20055,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>1339</v>
       </c>
@@ -20068,7 +20084,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>1342</v>
       </c>
@@ -20097,7 +20113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>1345</v>
       </c>
@@ -20126,7 +20142,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>1348</v>
       </c>
@@ -20155,7 +20171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>1350</v>
       </c>
@@ -20184,7 +20200,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>1353</v>
       </c>
@@ -20213,7 +20229,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>1356</v>
       </c>
@@ -20242,7 +20258,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>1359</v>
       </c>
@@ -20271,7 +20287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>1362</v>
       </c>
@@ -20300,7 +20316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>1365</v>
       </c>
@@ -20329,7 +20345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>1368</v>
       </c>
@@ -20358,7 +20374,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>1371</v>
       </c>
@@ -20387,7 +20403,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>1374</v>
       </c>
@@ -20416,7 +20432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>1376</v>
       </c>
@@ -20445,7 +20461,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>1379</v>
       </c>
@@ -20474,7 +20490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>1382</v>
       </c>
@@ -20503,7 +20519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>1385</v>
       </c>
@@ -20532,7 +20548,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>1388</v>
       </c>
@@ -20561,7 +20577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>1391</v>
       </c>
@@ -20590,7 +20606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>1394</v>
       </c>
@@ -20615,7 +20631,7 @@
       <c r="H465" s="2"/>
       <c r="I465" s="2"/>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>1397</v>
       </c>
@@ -20640,7 +20656,7 @@
       <c r="H466" s="2"/>
       <c r="I466" s="2"/>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>1400</v>
       </c>
@@ -20665,7 +20681,7 @@
       <c r="H467" s="2"/>
       <c r="I467" s="2"/>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>1403</v>
       </c>
@@ -20690,7 +20706,7 @@
       <c r="H468" s="2"/>
       <c r="I468" s="2"/>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>1406</v>
       </c>
@@ -20715,7 +20731,7 @@
       <c r="H469" s="2"/>
       <c r="I469" s="2"/>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>1409</v>
       </c>
@@ -20740,7 +20756,7 @@
       <c r="H470" s="2"/>
       <c r="I470" s="2"/>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>1412</v>
       </c>
@@ -20765,7 +20781,7 @@
       <c r="H471" s="2"/>
       <c r="I471" s="2"/>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>1415</v>
       </c>
@@ -20790,7 +20806,7 @@
       <c r="H472" s="2"/>
       <c r="I472" s="2"/>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>1418</v>
       </c>
@@ -20815,7 +20831,7 @@
       <c r="H473" s="2"/>
       <c r="I473" s="2"/>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>1421</v>
       </c>
@@ -20840,7 +20856,7 @@
       <c r="H474" s="2"/>
       <c r="I474" s="2"/>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>1424</v>
       </c>
@@ -20865,7 +20881,7 @@
       <c r="H475" s="2"/>
       <c r="I475" s="2"/>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>1427</v>
       </c>
@@ -20890,7 +20906,7 @@
       <c r="H476" s="2"/>
       <c r="I476" s="2"/>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>1429</v>
       </c>
@@ -20915,7 +20931,7 @@
       <c r="H477" s="2"/>
       <c r="I477" s="2"/>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>1431</v>
       </c>
@@ -20940,7 +20956,7 @@
       <c r="H478" s="2"/>
       <c r="I478" s="2"/>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>1434</v>
       </c>
@@ -20965,7 +20981,7 @@
       <c r="H479" s="2"/>
       <c r="I479" s="2"/>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>1437</v>
       </c>
@@ -20990,7 +21006,7 @@
       <c r="H480" s="2"/>
       <c r="I480" s="2"/>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>1440</v>
       </c>
@@ -21015,7 +21031,7 @@
       <c r="H481" s="2"/>
       <c r="I481" s="2"/>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>1443</v>
       </c>
@@ -21040,7 +21056,7 @@
       <c r="H482" s="2"/>
       <c r="I482" s="2"/>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>1446</v>
       </c>
@@ -21065,7 +21081,7 @@
       <c r="H483" s="2"/>
       <c r="I483" s="2"/>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>1449</v>
       </c>
@@ -21090,7 +21106,7 @@
       <c r="H484" s="2"/>
       <c r="I484" s="2"/>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>1451</v>
       </c>
@@ -21115,7 +21131,7 @@
       <c r="H485" s="2"/>
       <c r="I485" s="2"/>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>1453</v>
       </c>
@@ -21140,7 +21156,7 @@
       <c r="H486" s="2"/>
       <c r="I486" s="2"/>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>1456</v>
       </c>
@@ -21165,7 +21181,7 @@
       <c r="H487" s="2"/>
       <c r="I487" s="2"/>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>1458</v>
       </c>
@@ -21190,7 +21206,7 @@
       <c r="H488" s="2"/>
       <c r="I488" s="2"/>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>1461</v>
       </c>
@@ -21215,7 +21231,7 @@
       <c r="H489" s="2"/>
       <c r="I489" s="2"/>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>1464</v>
       </c>
@@ -21240,7 +21256,7 @@
       <c r="H490" s="2"/>
       <c r="I490" s="2"/>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>1467</v>
       </c>
@@ -21265,7 +21281,7 @@
       <c r="H491" s="2"/>
       <c r="I491" s="2"/>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>1470</v>
       </c>
@@ -21290,7 +21306,7 @@
       <c r="H492" s="2"/>
       <c r="I492" s="2"/>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>1473</v>
       </c>
@@ -21315,7 +21331,7 @@
       <c r="H493" s="2"/>
       <c r="I493" s="2"/>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>1476</v>
       </c>
@@ -21340,7 +21356,7 @@
       <c r="H494" s="2"/>
       <c r="I494" s="2"/>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>1479</v>
       </c>
@@ -21365,7 +21381,7 @@
       <c r="H495" s="2"/>
       <c r="I495" s="2"/>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>1482</v>
       </c>
@@ -21390,7 +21406,7 @@
       <c r="H496" s="2"/>
       <c r="I496" s="2"/>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>1485</v>
       </c>
@@ -21415,7 +21431,7 @@
       <c r="H497" s="2"/>
       <c r="I497" s="2"/>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>1488</v>
       </c>
@@ -21440,7 +21456,7 @@
       <c r="H498" s="2"/>
       <c r="I498" s="2"/>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>1491</v>
       </c>
@@ -21465,7 +21481,7 @@
       <c r="H499" s="2"/>
       <c r="I499" s="2"/>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>1494</v>
       </c>
@@ -21490,7 +21506,7 @@
       <c r="H500" s="2"/>
       <c r="I500" s="2"/>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>1497</v>
       </c>
@@ -21515,7 +21531,7 @@
       <c r="H501" s="2"/>
       <c r="I501" s="2"/>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>1500</v>
       </c>
@@ -21540,7 +21556,7 @@
       <c r="H502" s="2"/>
       <c r="I502" s="2"/>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>1503</v>
       </c>
@@ -21569,7 +21585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>1507</v>
       </c>
@@ -21594,7 +21610,7 @@
       <c r="H504" s="2"/>
       <c r="I504" s="2"/>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>1510</v>
       </c>
@@ -21615,7 +21631,7 @@
       <c r="H505" s="2"/>
       <c r="I505" s="2"/>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>1514</v>
       </c>
@@ -21644,7 +21660,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>1517</v>
       </c>
@@ -21669,7 +21685,7 @@
       <c r="H507" s="2"/>
       <c r="I507" s="2"/>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>1520</v>
       </c>
@@ -21694,7 +21710,7 @@
       <c r="H508" s="2"/>
       <c r="I508" s="2"/>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>1523</v>
       </c>
@@ -21715,7 +21731,7 @@
       <c r="H509" s="2"/>
       <c r="I509" s="2"/>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>1526</v>
       </c>
@@ -21736,7 +21752,7 @@
       <c r="H510" s="2"/>
       <c r="I510" s="2"/>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>1529</v>
       </c>
@@ -21757,7 +21773,7 @@
       <c r="H511" s="2"/>
       <c r="I511" s="2"/>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>1532</v>
       </c>
@@ -21782,7 +21798,7 @@
       <c r="H512" s="2"/>
       <c r="I512" s="2"/>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>1535</v>
       </c>
@@ -21807,7 +21823,7 @@
       <c r="H513" s="2"/>
       <c r="I513" s="2"/>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>1538</v>
       </c>
@@ -21832,7 +21848,7 @@
       <c r="H514" s="2"/>
       <c r="I514" s="2"/>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>1541</v>
       </c>
@@ -21853,7 +21869,7 @@
       <c r="H515" s="2"/>
       <c r="I515" s="2"/>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>1544</v>
       </c>
@@ -21878,7 +21894,7 @@
       <c r="H516" s="2"/>
       <c r="I516" s="2"/>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>1547</v>
       </c>
@@ -21903,7 +21919,7 @@
       <c r="H517" s="2"/>
       <c r="I517" s="2"/>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>1550</v>
       </c>
@@ -21932,7 +21948,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>1553</v>
       </c>
@@ -21953,7 +21969,7 @@
       <c r="H519" s="2"/>
       <c r="I519" s="2"/>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>1556</v>
       </c>
@@ -21978,7 +21994,7 @@
       <c r="H520" s="2"/>
       <c r="I520" s="2"/>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>1559</v>
       </c>
@@ -22003,7 +22019,7 @@
       <c r="H521" s="2"/>
       <c r="I521" s="2"/>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>1562</v>
       </c>
@@ -22030,7 +22046,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>1565</v>
       </c>
@@ -22051,7 +22067,7 @@
       <c r="H523" s="2"/>
       <c r="I523" s="2"/>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>1568</v>
       </c>
@@ -22080,7 +22096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>1571</v>
       </c>
@@ -22105,7 +22121,7 @@
       <c r="H525" s="2"/>
       <c r="I525" s="2"/>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>1574</v>
       </c>
@@ -22130,7 +22146,7 @@
       <c r="H526" s="2"/>
       <c r="I526" s="2"/>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>1577</v>
       </c>
@@ -22151,7 +22167,7 @@
       <c r="H527" s="2"/>
       <c r="I527" s="2"/>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>1580</v>
       </c>
@@ -22176,7 +22192,7 @@
       <c r="H528" s="2"/>
       <c r="I528" s="2"/>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>1583</v>
       </c>
@@ -22201,7 +22217,7 @@
       <c r="H529" s="2"/>
       <c r="I529" s="2"/>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>1586</v>
       </c>
@@ -22230,7 +22246,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>1589</v>
       </c>
@@ -22251,7 +22267,7 @@
       <c r="H531" s="2"/>
       <c r="I531" s="2"/>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>1592</v>
       </c>
@@ -22280,7 +22296,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>1595</v>
       </c>
@@ -22309,7 +22325,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>1597</v>
       </c>
@@ -22338,7 +22354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>1599</v>
       </c>
@@ -22359,7 +22375,7 @@
       <c r="H535" s="2"/>
       <c r="I535" s="2"/>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>1603</v>
       </c>
@@ -22380,7 +22396,7 @@
       <c r="H536" s="2"/>
       <c r="I536" s="2"/>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>1606</v>
       </c>
@@ -22401,7 +22417,7 @@
       <c r="H537" s="2"/>
       <c r="I537" s="2"/>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>1609</v>
       </c>
@@ -22422,7 +22438,7 @@
       <c r="H538" s="2"/>
       <c r="I538" s="2"/>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>1612</v>
       </c>
@@ -22443,7 +22459,7 @@
       <c r="H539" s="2"/>
       <c r="I539" s="2"/>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>1615</v>
       </c>
@@ -22464,7 +22480,7 @@
       <c r="H540" s="2"/>
       <c r="I540" s="2"/>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>1618</v>
       </c>
@@ -22485,7 +22501,7 @@
       <c r="H541" s="2"/>
       <c r="I541" s="2"/>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>1621</v>
       </c>
@@ -22506,7 +22522,7 @@
       <c r="H542" s="2"/>
       <c r="I542" s="2"/>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>1624</v>
       </c>
@@ -22527,7 +22543,7 @@
       <c r="H543" s="2"/>
       <c r="I543" s="2"/>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>1627</v>
       </c>
@@ -22556,7 +22572,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>1631</v>
       </c>
@@ -22577,7 +22593,7 @@
       <c r="H545" s="2"/>
       <c r="I545" s="2"/>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>1634</v>
       </c>
@@ -22602,7 +22618,7 @@
       <c r="H546" s="2"/>
       <c r="I546" s="2"/>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>1637</v>
       </c>
@@ -22623,7 +22639,7 @@
       <c r="H547" s="2"/>
       <c r="I547" s="2"/>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>1640</v>
       </c>
@@ -22652,7 +22668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>1644</v>
       </c>
@@ -22677,7 +22693,7 @@
       <c r="H549" s="2"/>
       <c r="I549" s="2"/>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>1647</v>
       </c>
@@ -22702,7 +22718,7 @@
       <c r="H550" s="2"/>
       <c r="I550" s="2"/>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>1650</v>
       </c>
@@ -22731,7 +22747,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>1654</v>
       </c>
@@ -22756,7 +22772,7 @@
       <c r="H552" s="2"/>
       <c r="I552" s="2"/>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>1657</v>
       </c>
@@ -22785,7 +22801,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>1660</v>
       </c>
@@ -22814,7 +22830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>1664</v>
       </c>
@@ -22843,7 +22859,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>1667</v>
       </c>
@@ -22864,7 +22880,7 @@
       <c r="H556" s="2"/>
       <c r="I556" s="2"/>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>1670</v>
       </c>
@@ -22889,7 +22905,7 @@
       <c r="H557" s="2"/>
       <c r="I557" s="2"/>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>1673</v>
       </c>
@@ -22914,7 +22930,7 @@
       <c r="H558" s="2"/>
       <c r="I558" s="2"/>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>1676</v>
       </c>
@@ -22939,7 +22955,7 @@
       <c r="H559" s="2"/>
       <c r="I559" s="2"/>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>1679</v>
       </c>
@@ -22968,7 +22984,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>1682</v>
       </c>
@@ -22997,7 +23013,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>1685</v>
       </c>
@@ -23022,7 +23038,7 @@
       <c r="H562" s="2"/>
       <c r="I562" s="2"/>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>1688</v>
       </c>
@@ -23051,7 +23067,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>1691</v>
       </c>
@@ -23080,7 +23096,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>1694</v>
       </c>
@@ -23105,7 +23121,7 @@
       <c r="H565" s="2"/>
       <c r="I565" s="2"/>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>1697</v>
       </c>
@@ -23130,7 +23146,7 @@
       <c r="H566" s="2"/>
       <c r="I566" s="2"/>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>1700</v>
       </c>
@@ -23155,7 +23171,7 @@
       <c r="H567" s="2"/>
       <c r="I567" s="2"/>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>1704</v>
       </c>
@@ -23180,7 +23196,7 @@
       <c r="H568" s="2"/>
       <c r="I568" s="2"/>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>1707</v>
       </c>
@@ -23209,7 +23225,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>1710</v>
       </c>
@@ -23234,7 +23250,7 @@
       <c r="H570" s="2"/>
       <c r="I570" s="2"/>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>1713</v>
       </c>
@@ -23263,7 +23279,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>1716</v>
       </c>
@@ -23288,7 +23304,7 @@
       <c r="H572" s="2"/>
       <c r="I572" s="2"/>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>1720</v>
       </c>
@@ -23317,7 +23333,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>1723</v>
       </c>
@@ -23346,7 +23362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>1726</v>
       </c>
@@ -23375,7 +23391,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>1729</v>
       </c>
@@ -23396,7 +23412,7 @@
       <c r="H576" s="2"/>
       <c r="I576" s="2"/>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>1732</v>
       </c>
@@ -23417,7 +23433,7 @@
       <c r="H577" s="2"/>
       <c r="I577" s="2"/>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>1735</v>
       </c>
@@ -23446,7 +23462,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>1738</v>
       </c>
@@ -23475,7 +23491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>1741</v>
       </c>
@@ -23504,7 +23520,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>1744</v>
       </c>
@@ -23533,7 +23549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>1747</v>
       </c>
@@ -23562,7 +23578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>1750</v>
       </c>
@@ -23591,7 +23607,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>1753</v>
       </c>
@@ -23620,7 +23636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>1756</v>
       </c>
@@ -23649,7 +23665,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>1759</v>
       </c>
@@ -23678,7 +23694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>1762</v>
       </c>
@@ -23703,7 +23719,7 @@
       <c r="H587" s="2"/>
       <c r="I587" s="2"/>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>1765</v>
       </c>
@@ -23724,7 +23740,7 @@
       <c r="H588" s="2"/>
       <c r="I588" s="2"/>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>1768</v>
       </c>
@@ -23745,7 +23761,7 @@
       <c r="H589" s="2"/>
       <c r="I589" s="2"/>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>1771</v>
       </c>
@@ -23770,7 +23786,7 @@
       <c r="H590" s="2"/>
       <c r="I590" s="2"/>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>1774</v>
       </c>
@@ -23791,7 +23807,7 @@
       <c r="H591" s="2"/>
       <c r="I591" s="2"/>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>1777</v>
       </c>
@@ -23816,7 +23832,7 @@
       <c r="H592" s="2"/>
       <c r="I592" s="2"/>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>1780</v>
       </c>
@@ -23841,7 +23857,7 @@
       <c r="H593" s="2"/>
       <c r="I593" s="2"/>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>1783</v>
       </c>
@@ -23870,7 +23886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>1786</v>
       </c>
@@ -23899,7 +23915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>1789</v>
       </c>
@@ -23928,7 +23944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>1792</v>
       </c>
@@ -23953,7 +23969,7 @@
       <c r="H597" s="2"/>
       <c r="I597" s="2"/>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>1795</v>
       </c>
@@ -23982,7 +23998,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>1798</v>
       </c>
@@ -24011,7 +24027,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>1801</v>
       </c>
@@ -24040,7 +24056,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>1804</v>
       </c>
@@ -24065,7 +24081,7 @@
       <c r="H601" s="2"/>
       <c r="I601" s="2"/>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>1807</v>
       </c>
@@ -24090,7 +24106,7 @@
       <c r="H602" s="2"/>
       <c r="I602" s="2"/>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>1810</v>
       </c>
@@ -24119,7 +24135,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>1813</v>
       </c>
@@ -24144,7 +24160,7 @@
       <c r="H604" s="2"/>
       <c r="I604" s="2"/>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>1816</v>
       </c>
@@ -24165,7 +24181,7 @@
       <c r="H605" s="2"/>
       <c r="I605" s="2"/>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>1819</v>
       </c>
@@ -24194,7 +24210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>1822</v>
       </c>
@@ -24215,7 +24231,7 @@
       <c r="H607" s="2"/>
       <c r="I607" s="2"/>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>1825</v>
       </c>
@@ -24244,7 +24260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>1828</v>
       </c>
@@ -24265,7 +24281,7 @@
       <c r="H609" s="2"/>
       <c r="I609" s="2"/>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>1831</v>
       </c>
@@ -24294,7 +24310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>1834</v>
       </c>
@@ -24319,7 +24335,7 @@
       <c r="H611" s="2"/>
       <c r="I611" s="2"/>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>1837</v>
       </c>
@@ -24348,7 +24364,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>1840</v>
       </c>
@@ -24377,7 +24393,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>1843</v>
       </c>
@@ -24406,7 +24422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>1846</v>
       </c>
@@ -24427,7 +24443,7 @@
       <c r="H615" s="2"/>
       <c r="I615" s="2"/>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>1849</v>
       </c>
@@ -24456,7 +24472,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>1852</v>
       </c>
@@ -24485,7 +24501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>1855</v>
       </c>
@@ -24506,7 +24522,7 @@
       <c r="H618" s="2"/>
       <c r="I618" s="2"/>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>1858</v>
       </c>
@@ -24535,7 +24551,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>1861</v>
       </c>
@@ -24560,7 +24576,7 @@
       <c r="H620" s="2"/>
       <c r="I620" s="2"/>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>1864</v>
       </c>
@@ -24589,7 +24605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>1867</v>
       </c>
@@ -24614,7 +24630,7 @@
       <c r="H622" s="2"/>
       <c r="I622" s="2"/>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>1870</v>
       </c>
@@ -24643,7 +24659,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>1873</v>
       </c>
@@ -24672,7 +24688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>1876</v>
       </c>
@@ -24701,7 +24717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>1879</v>
       </c>
@@ -24730,7 +24746,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>1882</v>
       </c>
@@ -24755,7 +24771,7 @@
       <c r="H627" s="2"/>
       <c r="I627" s="2"/>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>1885</v>
       </c>
@@ -24784,7 +24800,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>1888</v>
       </c>
@@ -24809,7 +24825,7 @@
       <c r="H629" s="2"/>
       <c r="I629" s="2"/>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>1891</v>
       </c>
@@ -24838,7 +24854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>1894</v>
       </c>
@@ -24867,7 +24883,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>1897</v>
       </c>
@@ -24892,7 +24908,7 @@
       <c r="H632" s="2"/>
       <c r="I632" s="2"/>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>1900</v>
       </c>
@@ -24917,7 +24933,7 @@
       <c r="H633" s="2"/>
       <c r="I633" s="2"/>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>1903</v>
       </c>
@@ -24942,7 +24958,7 @@
       <c r="H634" s="2"/>
       <c r="I634" s="2"/>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>1906</v>
       </c>
@@ -24963,7 +24979,7 @@
       <c r="H635" s="2"/>
       <c r="I635" s="2"/>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>1909</v>
       </c>
@@ -24992,7 +25008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>1912</v>
       </c>
@@ -25017,7 +25033,7 @@
       <c r="H637" s="2"/>
       <c r="I637" s="2"/>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>1915</v>
       </c>
@@ -25042,7 +25058,7 @@
       <c r="H638" s="2"/>
       <c r="I638" s="2"/>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>1918</v>
       </c>
@@ -25067,7 +25083,7 @@
       <c r="H639" s="2"/>
       <c r="I639" s="2"/>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>1921</v>
       </c>
@@ -25092,7 +25108,7 @@
       <c r="H640" s="2"/>
       <c r="I640" s="2"/>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>1924</v>
       </c>
@@ -25113,7 +25129,7 @@
       <c r="H641" s="2"/>
       <c r="I641" s="2"/>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>1927</v>
       </c>
@@ -25138,7 +25154,7 @@
       <c r="H642" s="2"/>
       <c r="I642" s="2"/>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>1930</v>
       </c>
@@ -25167,7 +25183,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>1933</v>
       </c>
@@ -25196,7 +25212,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>1936</v>
       </c>
@@ -25221,7 +25237,7 @@
       <c r="H645" s="2"/>
       <c r="I645" s="2"/>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>1939</v>
       </c>
@@ -25250,7 +25266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>1942</v>
       </c>
@@ -25275,7 +25291,7 @@
       <c r="H647" s="2"/>
       <c r="I647" s="2"/>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>1945</v>
       </c>
@@ -25296,7 +25312,7 @@
       <c r="H648" s="2"/>
       <c r="I648" s="2"/>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>1948</v>
       </c>
@@ -25325,7 +25341,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>1951</v>
       </c>
@@ -25350,7 +25366,7 @@
       <c r="H650" s="2"/>
       <c r="I650" s="2"/>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>1954</v>
       </c>
@@ -25375,7 +25391,7 @@
       <c r="H651" s="2"/>
       <c r="I651" s="2"/>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>1957</v>
       </c>
@@ -25404,7 +25420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>1960</v>
       </c>
@@ -25433,7 +25449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>1963</v>
       </c>
@@ -25458,7 +25474,7 @@
       <c r="H654" s="2"/>
       <c r="I654" s="2"/>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>1966</v>
       </c>
@@ -25487,7 +25503,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>1969</v>
       </c>
@@ -25508,7 +25524,7 @@
       <c r="H656" s="2"/>
       <c r="I656" s="2"/>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>1972</v>
       </c>
@@ -25537,7 +25553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>1975</v>
       </c>
@@ -25566,7 +25582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>1978</v>
       </c>
@@ -25591,7 +25607,7 @@
       <c r="H659" s="2"/>
       <c r="I659" s="2"/>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>1981</v>
       </c>
@@ -25612,7 +25628,7 @@
       <c r="H660" s="2"/>
       <c r="I660" s="2"/>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>1984</v>
       </c>
@@ -25641,7 +25657,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>1987</v>
       </c>
@@ -25662,7 +25678,7 @@
       <c r="H662" s="2"/>
       <c r="I662" s="2"/>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>1990</v>
       </c>
@@ -25691,7 +25707,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>1993</v>
       </c>
@@ -25712,7 +25728,7 @@
       <c r="H664" s="2"/>
       <c r="I664" s="2"/>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>1997</v>
       </c>
@@ -25741,7 +25757,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>2000</v>
       </c>
@@ -25770,7 +25786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>2003</v>
       </c>
@@ -25795,7 +25811,7 @@
       <c r="H667" s="2"/>
       <c r="I667" s="2"/>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>2006</v>
       </c>
@@ -25820,7 +25836,7 @@
       <c r="H668" s="2"/>
       <c r="I668" s="2"/>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>2009</v>
       </c>
@@ -25845,7 +25861,7 @@
       <c r="H669" s="2"/>
       <c r="I669" s="2"/>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>2012</v>
       </c>
@@ -25874,7 +25890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>2015</v>
       </c>
@@ -25899,7 +25915,7 @@
       <c r="H671" s="2"/>
       <c r="I671" s="2"/>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>2018</v>
       </c>
@@ -25928,7 +25944,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>2021</v>
       </c>
@@ -25953,7 +25969,7 @@
       <c r="H673" s="2"/>
       <c r="I673" s="2"/>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>2024</v>
       </c>
@@ -25978,7 +25994,7 @@
       <c r="H674" s="2"/>
       <c r="I674" s="2"/>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>2027</v>
       </c>
@@ -26007,7 +26023,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>2030</v>
       </c>
@@ -26032,7 +26048,7 @@
       <c r="H676" s="2"/>
       <c r="I676" s="2"/>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>2033</v>
       </c>
@@ -26057,7 +26073,7 @@
       <c r="H677" s="2"/>
       <c r="I677" s="2"/>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>2036</v>
       </c>
@@ -26082,7 +26098,7 @@
       <c r="H678" s="2"/>
       <c r="I678" s="2"/>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>2039</v>
       </c>
@@ -26107,7 +26123,7 @@
       <c r="H679" s="2"/>
       <c r="I679" s="2"/>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>2042</v>
       </c>
@@ -26132,7 +26148,7 @@
       <c r="H680" s="2"/>
       <c r="I680" s="2"/>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>2045</v>
       </c>
@@ -26161,7 +26177,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>2048</v>
       </c>
@@ -26190,7 +26206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>2051</v>
       </c>
@@ -26219,7 +26235,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>2054</v>
       </c>
@@ -26248,7 +26264,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>2057</v>
       </c>
@@ -26277,7 +26293,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>2060</v>
       </c>
@@ -26302,7 +26318,7 @@
       <c r="H686" s="2"/>
       <c r="I686" s="2"/>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>2063</v>
       </c>
@@ -26327,7 +26343,7 @@
       <c r="H687" s="2"/>
       <c r="I687" s="2"/>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>2066</v>
       </c>
@@ -26356,7 +26372,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>2069</v>
       </c>
@@ -26385,7 +26401,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>2072</v>
       </c>
@@ -26410,7 +26426,7 @@
       <c r="H690" s="2"/>
       <c r="I690" s="2"/>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>2075</v>
       </c>
@@ -26435,7 +26451,7 @@
       <c r="H691" s="2"/>
       <c r="I691" s="2"/>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>2078</v>
       </c>
@@ -26462,7 +26478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>2080</v>
       </c>
@@ -26491,7 +26507,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>2083</v>
       </c>
@@ -26516,7 +26532,7 @@
       <c r="H694" s="2"/>
       <c r="I694" s="2"/>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>2086</v>
       </c>
@@ -26541,7 +26557,7 @@
       <c r="H695" s="2"/>
       <c r="I695" s="2"/>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>2089</v>
       </c>
@@ -26570,7 +26586,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>2092</v>
       </c>
@@ -26599,7 +26615,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>2095</v>
       </c>
@@ -26628,7 +26644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>2098</v>
       </c>
@@ -26657,7 +26673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>2101</v>
       </c>
@@ -26686,7 +26702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>2104</v>
       </c>
@@ -26715,7 +26731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>2107</v>
       </c>
@@ -26744,7 +26760,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>2110</v>
       </c>
@@ -26773,7 +26789,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>2113</v>
       </c>
@@ -26798,7 +26814,7 @@
       <c r="H704" s="2"/>
       <c r="I704" s="2"/>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>2116</v>
       </c>
@@ -26823,7 +26839,7 @@
       <c r="H705" s="2"/>
       <c r="I705" s="2"/>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>2119</v>
       </c>
@@ -26848,7 +26864,7 @@
       <c r="H706" s="2"/>
       <c r="I706" s="2"/>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>2122</v>
       </c>
@@ -26873,7 +26889,7 @@
       <c r="H707" s="2"/>
       <c r="I707" s="2"/>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>2125</v>
       </c>
@@ -26902,7 +26918,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>2128</v>
       </c>
@@ -26931,7 +26947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>2131</v>
       </c>
@@ -26960,7 +26976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>2134</v>
       </c>
@@ -26989,7 +27005,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>2137</v>
       </c>
@@ -27014,7 +27030,7 @@
       <c r="H712" s="2"/>
       <c r="I712" s="2"/>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>2140</v>
       </c>
@@ -27039,7 +27055,7 @@
       <c r="H713" s="2"/>
       <c r="I713" s="2"/>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>2143</v>
       </c>
@@ -27064,7 +27080,7 @@
       <c r="H714" s="2"/>
       <c r="I714" s="2"/>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>2146</v>
       </c>
@@ -27089,7 +27105,7 @@
       <c r="H715" s="2"/>
       <c r="I715" s="2"/>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>2149</v>
       </c>
@@ -27114,7 +27130,7 @@
       <c r="H716" s="2"/>
       <c r="I716" s="2"/>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>2152</v>
       </c>
@@ -27143,7 +27159,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>2155</v>
       </c>
@@ -27172,7 +27188,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>2158</v>
       </c>
@@ -27201,7 +27217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>2161</v>
       </c>
@@ -27230,7 +27246,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>2164</v>
       </c>
@@ -27259,7 +27275,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>2167</v>
       </c>
@@ -27288,7 +27304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>2170</v>
       </c>
@@ -27317,7 +27333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>2173</v>
       </c>
@@ -27346,7 +27362,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>2176</v>
       </c>
@@ -27375,7 +27391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>2179</v>
       </c>
@@ -27400,7 +27416,7 @@
       <c r="H726" s="2"/>
       <c r="I726" s="2"/>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>2182</v>
       </c>
@@ -27425,7 +27441,7 @@
       <c r="H727" s="2"/>
       <c r="I727" s="2"/>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>2185</v>
       </c>
@@ -27450,7 +27466,7 @@
       <c r="H728" s="2"/>
       <c r="I728" s="2"/>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>2188</v>
       </c>
@@ -27475,7 +27491,7 @@
       <c r="H729" s="2"/>
       <c r="I729" s="2"/>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>2191</v>
       </c>
@@ -27500,7 +27516,7 @@
       <c r="H730" s="2"/>
       <c r="I730" s="2"/>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>2194</v>
       </c>
@@ -27529,7 +27545,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>2197</v>
       </c>
@@ -27558,7 +27574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>2200</v>
       </c>
@@ -27587,7 +27603,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>2203</v>
       </c>
@@ -27616,7 +27632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>2206</v>
       </c>
@@ -27645,7 +27661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>2209</v>
       </c>
@@ -27674,7 +27690,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>2212</v>
       </c>
@@ -27703,7 +27719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>2215</v>
       </c>
@@ -27732,7 +27748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>2218</v>
       </c>
@@ -27757,7 +27773,7 @@
       <c r="H739" s="2"/>
       <c r="I739" s="2"/>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>2221</v>
       </c>
@@ -27782,7 +27798,7 @@
       <c r="H740" s="2"/>
       <c r="I740" s="2"/>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>2224</v>
       </c>
@@ -27807,7 +27823,7 @@
       <c r="H741" s="2"/>
       <c r="I741" s="2"/>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>2227</v>
       </c>
@@ -27832,7 +27848,7 @@
       <c r="H742" s="2"/>
       <c r="I742" s="2"/>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>2230</v>
       </c>
@@ -27857,7 +27873,7 @@
       <c r="H743" s="2"/>
       <c r="I743" s="2"/>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>2233</v>
       </c>
@@ -27882,7 +27898,7 @@
       <c r="H744" s="2"/>
       <c r="I744" s="2"/>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>2236</v>
       </c>
@@ -27907,7 +27923,7 @@
       <c r="H745" s="2"/>
       <c r="I745" s="2"/>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>2239</v>
       </c>
@@ -27936,7 +27952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>2242</v>
       </c>
@@ -27965,7 +27981,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>2245</v>
       </c>
@@ -27994,7 +28010,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>2248</v>
       </c>
@@ -28023,7 +28039,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>2251</v>
       </c>
@@ -28052,7 +28068,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>2254</v>
       </c>
@@ -28081,7 +28097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>2257</v>
       </c>
@@ -28106,7 +28122,7 @@
       <c r="H752" s="2"/>
       <c r="I752" s="2"/>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>2260</v>
       </c>
@@ -28135,7 +28151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>2263</v>
       </c>
@@ -28160,7 +28176,7 @@
       <c r="H754" s="2"/>
       <c r="I754" s="2"/>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>2266</v>
       </c>
@@ -28185,7 +28201,7 @@
       <c r="H755" s="2"/>
       <c r="I755" s="2"/>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>2269</v>
       </c>
@@ -28210,7 +28226,7 @@
       <c r="H756" s="2"/>
       <c r="I756" s="2"/>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>2272</v>
       </c>
@@ -28235,7 +28251,7 @@
       <c r="H757" s="2"/>
       <c r="I757" s="2"/>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>2275</v>
       </c>
@@ -28264,7 +28280,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>2278</v>
       </c>
@@ -28293,7 +28309,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>2281</v>
       </c>
@@ -28322,7 +28338,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>2284</v>
       </c>
@@ -28351,7 +28367,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>2287</v>
       </c>
@@ -28380,7 +28396,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>2290</v>
       </c>
@@ -28409,7 +28425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>2293</v>
       </c>
@@ -28438,7 +28454,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>2296</v>
       </c>
@@ -28463,7 +28479,7 @@
       <c r="H765" s="2"/>
       <c r="I765" s="2"/>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>2299</v>
       </c>
@@ -28488,7 +28504,7 @@
       <c r="H766" s="2"/>
       <c r="I766" s="2"/>
     </row>
-    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>2302</v>
       </c>
@@ -28513,7 +28529,7 @@
       <c r="H767" s="2"/>
       <c r="I767" s="2"/>
     </row>
-    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>2305</v>
       </c>
@@ -28538,7 +28554,7 @@
       <c r="H768" s="2"/>
       <c r="I768" s="2"/>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>2308</v>
       </c>
@@ -28563,7 +28579,7 @@
       <c r="H769" s="2"/>
       <c r="I769" s="2"/>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>2311</v>
       </c>
@@ -28592,7 +28608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>2314</v>
       </c>
@@ -28621,7 +28637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>2317</v>
       </c>
@@ -28650,7 +28666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>2320</v>
       </c>
@@ -28679,7 +28695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>2323</v>
       </c>
@@ -28708,7 +28724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>2326</v>
       </c>
@@ -28733,7 +28749,7 @@
       <c r="H775" s="2"/>
       <c r="I775" s="2"/>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>2329</v>
       </c>
@@ -28758,7 +28774,7 @@
       <c r="H776" s="2"/>
       <c r="I776" s="2"/>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>2332</v>
       </c>
@@ -28787,7 +28803,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>2335</v>
       </c>
@@ -28816,7 +28832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>2338</v>
       </c>
@@ -28845,7 +28861,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>2341</v>
       </c>
@@ -28870,7 +28886,7 @@
       <c r="H780" s="2"/>
       <c r="I780" s="2"/>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>2344</v>
       </c>
@@ -28895,7 +28911,7 @@
       <c r="H781" s="2"/>
       <c r="I781" s="2"/>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>2347</v>
       </c>
@@ -28920,7 +28936,7 @@
       <c r="H782" s="2"/>
       <c r="I782" s="2"/>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>2350</v>
       </c>
@@ -28945,7 +28961,7 @@
       <c r="H783" s="2"/>
       <c r="I783" s="2"/>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>2353</v>
       </c>
@@ -28974,7 +28990,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>2356</v>
       </c>
@@ -29003,7 +29019,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>2359</v>
       </c>
@@ -29032,7 +29048,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>2362</v>
       </c>
@@ -29057,7 +29073,7 @@
       <c r="H787" s="2"/>
       <c r="I787" s="2"/>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>2365</v>
       </c>
@@ -29082,7 +29098,7 @@
       <c r="H788" s="2"/>
       <c r="I788" s="2"/>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>2368</v>
       </c>
@@ -29107,7 +29123,7 @@
       <c r="H789" s="2"/>
       <c r="I789" s="2"/>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>2371</v>
       </c>
@@ -29136,7 +29152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>2374</v>
       </c>
@@ -29165,7 +29181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>2377</v>
       </c>
@@ -29194,7 +29210,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>2380</v>
       </c>
@@ -29223,7 +29239,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>2383</v>
       </c>
@@ -29252,7 +29268,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>2386</v>
       </c>
@@ -29281,7 +29297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>2389</v>
       </c>
@@ -29310,7 +29326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>2392</v>
       </c>
@@ -29339,7 +29355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>2395</v>
       </c>
@@ -29364,7 +29380,7 @@
       <c r="H798" s="2"/>
       <c r="I798" s="2"/>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>2398</v>
       </c>
@@ -29389,7 +29405,7 @@
       <c r="H799" s="2"/>
       <c r="I799" s="2"/>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>2401</v>
       </c>
@@ -29418,7 +29434,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>2404</v>
       </c>
@@ -29447,7 +29463,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>2407</v>
       </c>
@@ -29476,7 +29492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>2410</v>
       </c>
@@ -29501,7 +29517,7 @@
       <c r="H803" s="2"/>
       <c r="I803" s="2"/>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>2413</v>
       </c>
@@ -29526,7 +29542,7 @@
       <c r="H804" s="2"/>
       <c r="I804" s="2"/>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>2416</v>
       </c>
@@ -29551,7 +29567,7 @@
       <c r="H805" s="2"/>
       <c r="I805" s="2"/>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>2419</v>
       </c>
@@ -29576,7 +29592,7 @@
       <c r="H806" s="2"/>
       <c r="I806" s="2"/>
     </row>
-    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>2422</v>
       </c>
@@ -29605,7 +29621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>2425</v>
       </c>
@@ -29634,7 +29650,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>2428</v>
       </c>
@@ -29663,7 +29679,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>2431</v>
       </c>
@@ -29688,7 +29704,7 @@
       <c r="H810" s="2"/>
       <c r="I810" s="2"/>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>2434</v>
       </c>
@@ -29717,7 +29733,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>2437</v>
       </c>
@@ -29746,7 +29762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>2440</v>
       </c>
@@ -29775,7 +29791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>2443</v>
       </c>
@@ -29800,7 +29816,7 @@
       <c r="H814" s="2"/>
       <c r="I814" s="2"/>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>2446</v>
       </c>
@@ -29825,7 +29841,7 @@
       <c r="H815" s="2"/>
       <c r="I815" s="2"/>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>2449</v>
       </c>
@@ -29850,7 +29866,7 @@
       <c r="H816" s="2"/>
       <c r="I816" s="2"/>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>2452</v>
       </c>
@@ -29879,7 +29895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>2455</v>
       </c>
@@ -29904,7 +29920,7 @@
       <c r="H818" s="2"/>
       <c r="I818" s="2"/>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>2458</v>
       </c>
@@ -29929,7 +29945,7 @@
       <c r="H819" s="2"/>
       <c r="I819" s="2"/>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>2461</v>
       </c>
@@ -29954,7 +29970,7 @@
       <c r="H820" s="2"/>
       <c r="I820" s="2"/>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>2464</v>
       </c>
@@ -29983,7 +29999,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>2467</v>
       </c>
@@ -30010,7 +30026,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>2469</v>
       </c>
@@ -30039,7 +30055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>2472</v>
       </c>
@@ -30068,7 +30084,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>2475</v>
       </c>
@@ -30093,7 +30109,7 @@
       <c r="H825" s="2"/>
       <c r="I825" s="2"/>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>2478</v>
       </c>
@@ -30118,7 +30134,7 @@
       <c r="H826" s="2"/>
       <c r="I826" s="2"/>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>2481</v>
       </c>
@@ -30147,7 +30163,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>2484</v>
       </c>
@@ -30176,7 +30192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>2487</v>
       </c>
@@ -30197,7 +30213,7 @@
       <c r="H829" s="2"/>
       <c r="I829" s="2"/>
     </row>
-    <row r="830" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>2490</v>
       </c>
@@ -30220,7 +30236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="831" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>2494</v>
       </c>
@@ -30243,7 +30259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="832" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>2497</v>
       </c>
@@ -30266,9 +30282,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
-        <v>2500</v>
+        <v>2506</v>
       </c>
       <c r="B833" t="s">
         <v>18</v>
@@ -30277,13 +30293,13 @@
         <v>168</v>
       </c>
       <c r="D833" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="E833" t="s">
         <v>2492</v>
       </c>
       <c r="F833" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="G833">
         <v>1</v>
@@ -30295,9 +30311,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="834" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B834" t="s">
         <v>112</v>
@@ -30306,16 +30322,62 @@
         <v>168</v>
       </c>
       <c r="D834" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="E834" t="s">
         <v>1225</v>
       </c>
       <c r="F834" t="s">
+        <v>2504</v>
+      </c>
+      <c r="G834">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="835" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A835" t="s">
         <v>2505</v>
       </c>
-      <c r="G834">
-        <v>1</v>
+      <c r="B835" t="s">
+        <v>10</v>
+      </c>
+      <c r="D835" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E835" t="s">
+        <v>2492</v>
+      </c>
+      <c r="F835" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="836" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A836" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B836" t="s">
+        <v>18</v>
+      </c>
+      <c r="C836" t="s">
+        <v>27</v>
+      </c>
+      <c r="D836" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E836" t="s">
+        <v>2509</v>
+      </c>
+      <c r="F836" t="s">
+        <v>2510</v>
+      </c>
+      <c r="G836">
+        <v>4</v>
+      </c>
+      <c r="H836">
+        <v>4</v>
+      </c>
+      <c r="I836">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/cards_template_excel.xlsx
+++ b/cards_template_excel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84240D90-7A1C-496C-93C7-AB221100613E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDB243B-1551-4B03-A17D-5EE98C1FE889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4951" uniqueCount="2511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4974" uniqueCount="2523">
   <si>
     <t>Name</t>
   </si>
@@ -7548,6 +7548,42 @@
   </si>
   <si>
     <t>zoe.jpg</t>
+  </si>
+  <si>
+    <t>Starchy</t>
+  </si>
+  <si>
+    <t>starchy.jpg</t>
+  </si>
+  <si>
+    <t>Once per turn, you may remove target Creature in a discard pile from the game and draw a card.</t>
+  </si>
+  <si>
+    <t>Sweet Delicious Meats</t>
+  </si>
+  <si>
+    <t>Target player heals 1 HP for each card that is removed from the game.</t>
+  </si>
+  <si>
+    <t>sweet_delicious_meats.jpg</t>
+  </si>
+  <si>
+    <t>Probably Too Many Unicorns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When this Creature enters play, reveal the bottom 4 cards of target player's deck. Put all Creatures revealed into their discard pile and the rest on top of their deck in any order. If this Creature is defeated, put it on the bottom of your deck. </t>
+  </si>
+  <si>
+    <t>probably_too_many_unicorns.jpg</t>
+  </si>
+  <si>
+    <t>Time Drake</t>
+  </si>
+  <si>
+    <t>time_drake.jpg</t>
+  </si>
+  <si>
+    <t>When Time Drake enters play, reveal the top 5 cards of target player's deck. Put all Creatures revealed into their discard pile and return the rest to the top of their deck in any order. Add an :attack_token: to Time Drake for each Creature put into a discard pile this way.</t>
   </si>
 </sst>
 </file>
@@ -7889,11 +7925,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I836"/>
+  <dimension ref="A1:I840"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.6640625" customWidth="1"/>
+    <col min="1" max="1" width="28.109375" customWidth="1"/>
     <col min="4" max="4" width="82.5546875" customWidth="1"/>
+    <col min="6" max="6" width="27.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -30380,6 +30417,104 @@
         <v>11</v>
       </c>
     </row>
+    <row r="837" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A837" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B837" t="s">
+        <v>10</v>
+      </c>
+      <c r="D837" t="s">
+        <v>2513</v>
+      </c>
+      <c r="E837" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F837" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="838" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A838" t="s">
+        <v>2514</v>
+      </c>
+      <c r="B838" t="s">
+        <v>112</v>
+      </c>
+      <c r="C838" t="s">
+        <v>168</v>
+      </c>
+      <c r="D838" t="s">
+        <v>2515</v>
+      </c>
+      <c r="E838" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F838" t="s">
+        <v>2516</v>
+      </c>
+      <c r="G838">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="839" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A839" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B839" t="s">
+        <v>18</v>
+      </c>
+      <c r="C839" t="s">
+        <v>168</v>
+      </c>
+      <c r="D839" t="s">
+        <v>2518</v>
+      </c>
+      <c r="E839" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F839" t="s">
+        <v>2519</v>
+      </c>
+      <c r="G839">
+        <v>1</v>
+      </c>
+      <c r="H839">
+        <v>1</v>
+      </c>
+      <c r="I839">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="840" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A840" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B840" t="s">
+        <v>18</v>
+      </c>
+      <c r="C840" t="s">
+        <v>168</v>
+      </c>
+      <c r="D840" t="s">
+        <v>2522</v>
+      </c>
+      <c r="E840" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F840" t="s">
+        <v>2521</v>
+      </c>
+      <c r="G840">
+        <v>2</v>
+      </c>
+      <c r="H840">
+        <v>0</v>
+      </c>
+      <c r="I840">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/cards_template_excel.xlsx
+++ b/cards_template_excel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDB243B-1551-4B03-A17D-5EE98C1FE889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DC89CE-6B1B-4BF0-8024-65333E4FBCA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4974" uniqueCount="2523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4984" uniqueCount="2528">
   <si>
     <t>Name</t>
   </si>
@@ -7584,6 +7584,21 @@
   </si>
   <si>
     <t>When Time Drake enters play, reveal the top 5 cards of target player's deck. Put all Creatures revealed into their discard pile and return the rest to the top of their deck in any order. Add an :attack_token: to Time Drake for each Creature put into a discard pile this way.</t>
+  </si>
+  <si>
+    <t>Me-Mow</t>
+  </si>
+  <si>
+    <t>During each of your turns, the first time you deal exactly 1 damage to an opposing Creature, remove the bottom card of target opponent's deck from the game. (Limit: Once per opposing Creature per turn.)</t>
+  </si>
+  <si>
+    <t>me-mow.jpg</t>
+  </si>
+  <si>
+    <t>Flame Princess Promo</t>
+  </si>
+  <si>
+    <t>flame_princess_promo.jpg</t>
   </si>
 </sst>
 </file>
@@ -7925,7 +7940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I840"/>
+  <dimension ref="A1:I842"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.109375" customWidth="1"/>
@@ -30515,6 +30530,40 @@
         <v>8</v>
       </c>
     </row>
+    <row r="841" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A841" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B841" t="s">
+        <v>10</v>
+      </c>
+      <c r="D841" t="s">
+        <v>2524</v>
+      </c>
+      <c r="E841" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F841" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="842" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A842" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B842" t="s">
+        <v>10</v>
+      </c>
+      <c r="D842" t="s">
+        <v>1733</v>
+      </c>
+      <c r="E842" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F842" t="s">
+        <v>2527</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
